--- a/backtest_runs/20260410_193731/by_symbol/JSGBETF/JSGBETF.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/JSGBETF/JSGBETF.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-4204.800000000003</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>95795.2</v>
@@ -679,7 +679,7 @@
         <v>-7056.000000000008</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>88739.19999999998</v>
@@ -817,7 +817,7 @@
         <v>-1440</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>94009.60000000001</v>
@@ -863,7 +863,7 @@
         <v>-57.600000000009</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>93952</v>
@@ -909,7 +909,7 @@
         <v>-3225.599999999993</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>90726.40000000001</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>90726.40000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-1036.799999999998</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>92828.79999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-2160</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>91935.99999999999</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>91935.99999999999</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>91935.99999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-2764.800000000002</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>95075.2</v>
@@ -1507,7 +1507,7 @@
         <v>-57.600000000009</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>95420.79999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-547.1999999999935</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>94873.60000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-777.600000000009</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>104377.6</v>
